--- a/public/sap-reporting/expansion-150-downloads/EXT-QM05-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-QM05-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R3faf5914480d44c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R1374e6b9e7174194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rf575a9ff56f1491e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R5a7cbc3fe10049e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rfacaa0e70317487b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Ra5d3da3c43a94a34"/>
   </x:sheets>
 </x:workbook>
 </file>
